--- a/exports/2ce4ac57-b500-4e37-ac53-f80371a55585_analysis.xlsx
+++ b/exports/2ce4ac57-b500-4e37-ac53-f80371a55585_analysis.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K128"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,7 +459,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>155</v>
+        <v>122</v>
       </c>
     </row>
     <row r="6">
@@ -524,21 +524,21 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>800001</v>
+        <v>54</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -548,20 +548,20 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>3.15</v>
+        <v>6.649</v>
       </c>
       <c r="I7" t="n">
-        <v>1.65</v>
+        <v>7.099</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5</v>
+        <v>0.45</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8">
@@ -569,21 +569,21 @@
         <v>2</v>
       </c>
       <c r="B8" t="n">
-        <v>147</v>
+        <v>96</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -593,20 +593,20 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>6.649</v>
+        <v>9.849</v>
       </c>
       <c r="I8" t="n">
-        <v>7.099</v>
+        <v>10.149</v>
       </c>
       <c r="J8" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="K8" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="9">
@@ -614,21 +614,21 @@
         <v>3</v>
       </c>
       <c r="B9" t="n">
-        <v>254</v>
+        <v>113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -638,20 +638,20 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>86.7%</t>
+          <t>84.2%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>9.849</v>
+        <v>12.149</v>
       </c>
       <c r="I9" t="n">
-        <v>10.149</v>
+        <v>12.699</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="K9" t="n">
-        <v>60</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="10">
@@ -659,21 +659,21 @@
         <v>4</v>
       </c>
       <c r="B10" t="n">
-        <v>300</v>
+        <v>183</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -683,20 +683,20 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>84.2%</t>
+          <t>77.0%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>12.149</v>
+        <v>20.948</v>
       </c>
       <c r="I10" t="n">
-        <v>12.699</v>
+        <v>21.198</v>
       </c>
       <c r="J10" t="n">
-        <v>0.55</v>
+        <v>0.25</v>
       </c>
       <c r="K10" t="n">
-        <v>32.7</v>
+        <v>72</v>
       </c>
     </row>
     <row r="11">
@@ -704,21 +704,21 @@
         <v>5</v>
       </c>
       <c r="B11" t="n">
-        <v>554</v>
+        <v>201</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -728,20 +728,20 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>77.0%</t>
+          <t>90.0%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>20.948</v>
+        <v>25.298</v>
       </c>
       <c r="I11" t="n">
-        <v>21.198</v>
+        <v>25.798</v>
       </c>
       <c r="J11" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="K11" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -749,21 +749,21 @@
         <v>6</v>
       </c>
       <c r="B12" t="n">
-        <v>641</v>
+        <v>247</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -773,20 +773,20 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>90.0%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>25.298</v>
+        <v>30.247</v>
       </c>
       <c r="I12" t="n">
-        <v>25.798</v>
+        <v>30.847</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="K12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13">
@@ -794,21 +794,21 @@
         <v>7</v>
       </c>
       <c r="B13" t="n">
-        <v>802</v>
+        <v>21</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -818,20 +818,20 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>70.2%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>30.247</v>
+        <v>34.047</v>
       </c>
       <c r="I13" t="n">
-        <v>30.847</v>
+        <v>34.447</v>
       </c>
       <c r="J13" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="K13" t="n">
-        <v>30</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14">
@@ -839,21 +839,21 @@
         <v>8</v>
       </c>
       <c r="B14" t="n">
-        <v>800014</v>
+        <v>98</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -863,20 +863,20 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>31.647</v>
+        <v>41.446</v>
       </c>
       <c r="I14" t="n">
-        <v>31.797</v>
+        <v>41.946</v>
       </c>
       <c r="J14" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="K14" t="n">
-        <v>120</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -884,21 +884,21 @@
         <v>9</v>
       </c>
       <c r="B15" t="n">
-        <v>856</v>
+        <v>124</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -908,14 +908,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>70.2%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>34.047</v>
+        <v>42.596</v>
       </c>
       <c r="I15" t="n">
-        <v>34.447</v>
+        <v>42.996</v>
       </c>
       <c r="J15" t="n">
         <v>0.4</v>
@@ -929,7 +929,7 @@
         <v>10</v>
       </c>
       <c r="B16" t="n">
-        <v>1038</v>
+        <v>140</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -953,20 +953,20 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>41.446</v>
+        <v>44.446</v>
       </c>
       <c r="I16" t="n">
-        <v>41.946</v>
+        <v>45.346</v>
       </c>
       <c r="J16" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="K16" t="n">
-        <v>36</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
@@ -974,21 +974,21 @@
         <v>11</v>
       </c>
       <c r="B17" t="n">
-        <v>1094</v>
+        <v>165</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -998,20 +998,20 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>91.8%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>42.596</v>
+        <v>45.946</v>
       </c>
       <c r="I17" t="n">
-        <v>42.996</v>
+        <v>46.296</v>
       </c>
       <c r="J17" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="K17" t="n">
-        <v>45</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="18">
@@ -1019,7 +1019,7 @@
         <v>12</v>
       </c>
       <c r="B18" t="n">
-        <v>1121</v>
+        <v>186</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -1043,20 +1043,20 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>60.5%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>44.446</v>
+        <v>47.546</v>
       </c>
       <c r="I18" t="n">
-        <v>45.346</v>
+        <v>47.846</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
       <c r="K18" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
     </row>
     <row r="19">
@@ -1064,21 +1064,21 @@
         <v>13</v>
       </c>
       <c r="B19" t="n">
-        <v>800018</v>
+        <v>202</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1088,20 +1088,20 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>44.846</v>
+        <v>49.596</v>
       </c>
       <c r="I19" t="n">
-        <v>45.146</v>
+        <v>50.146</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="K19" t="n">
-        <v>60</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="20">
@@ -1109,21 +1109,21 @@
         <v>14</v>
       </c>
       <c r="B20" t="n">
-        <v>1207</v>
+        <v>231</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1133,14 +1133,14 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>91.8%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>45.946</v>
+        <v>50.596</v>
       </c>
       <c r="I20" t="n">
-        <v>46.296</v>
+        <v>50.946</v>
       </c>
       <c r="J20" t="n">
         <v>0.35</v>
@@ -1154,21 +1154,21 @@
         <v>15</v>
       </c>
       <c r="B21" t="n">
-        <v>1263</v>
+        <v>19</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1178,20 +1178,20 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>60.5%</t>
+          <t>33.4%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>47.546</v>
+        <v>52.045</v>
       </c>
       <c r="I21" t="n">
-        <v>47.846</v>
+        <v>52.595</v>
       </c>
       <c r="J21" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="K21" t="n">
-        <v>60</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="22">
@@ -1199,21 +1199,21 @@
         <v>16</v>
       </c>
       <c r="B22" t="n">
-        <v>1284</v>
+        <v>60</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1223,20 +1223,20 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>49.596</v>
+        <v>52.845</v>
       </c>
       <c r="I22" t="n">
-        <v>50.146</v>
+        <v>53.295</v>
       </c>
       <c r="J22" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="K22" t="n">
-        <v>32.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="23">
@@ -1244,21 +1244,21 @@
         <v>17</v>
       </c>
       <c r="B23" t="n">
-        <v>1313</v>
+        <v>65</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1268,20 +1268,20 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>50.596</v>
+        <v>63.194</v>
       </c>
       <c r="I23" t="n">
-        <v>50.946</v>
+        <v>53.045</v>
       </c>
       <c r="J23" t="n">
-        <v>0.35</v>
+        <v>10.149</v>
       </c>
       <c r="K23" t="n">
-        <v>51.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="24">
@@ -1289,21 +1289,21 @@
         <v>18</v>
       </c>
       <c r="B24" t="n">
-        <v>1333</v>
+        <v>73</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1313,20 +1313,20 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>33.4%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>52.045</v>
+        <v>53.645</v>
       </c>
       <c r="I24" t="n">
-        <v>52.595</v>
+        <v>54.095</v>
       </c>
       <c r="J24" t="n">
-        <v>0.55</v>
+        <v>0.45</v>
       </c>
       <c r="K24" t="n">
-        <v>32.7</v>
+        <v>40</v>
       </c>
     </row>
     <row r="25">
@@ -1334,7 +1334,7 @@
         <v>19</v>
       </c>
       <c r="B25" t="n">
-        <v>1355</v>
+        <v>130</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1353,25 +1353,25 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>opposite</t>
+          <t>normal</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>52.595</v>
+        <v>55.495</v>
       </c>
       <c r="I25" t="n">
-        <v>53.045</v>
+        <v>56.495</v>
       </c>
       <c r="J25" t="n">
-        <v>0.45</v>
+        <v>1</v>
       </c>
       <c r="K25" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26">
@@ -1379,21 +1379,21 @@
         <v>20</v>
       </c>
       <c r="B26" t="n">
-        <v>1372</v>
+        <v>133</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1403,20 +1403,20 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>52.845</v>
+        <v>56.695</v>
       </c>
       <c r="I26" t="n">
-        <v>53.295</v>
+        <v>57.195</v>
       </c>
       <c r="J26" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="K26" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27">
@@ -1424,21 +1424,21 @@
         <v>21</v>
       </c>
       <c r="B27" t="n">
-        <v>1382</v>
+        <v>240</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1448,14 +1448,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>77.2%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>53.645</v>
+        <v>59.845</v>
       </c>
       <c r="I27" t="n">
-        <v>54.095</v>
+        <v>60.295</v>
       </c>
       <c r="J27" t="n">
         <v>0.45</v>
@@ -1469,7 +1469,7 @@
         <v>22</v>
       </c>
       <c r="B28" t="n">
-        <v>1406</v>
+        <v>248</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -1493,20 +1493,20 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>76.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>54.795</v>
+        <v>60.395</v>
       </c>
       <c r="I28" t="n">
-        <v>55.295</v>
+        <v>60.745</v>
       </c>
       <c r="J28" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="K28" t="n">
-        <v>36</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="29">
@@ -1514,21 +1514,21 @@
         <v>23</v>
       </c>
       <c r="B29" t="n">
-        <v>1440</v>
+        <v>7</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1538,20 +1538,20 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>81.1%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>56.145</v>
+        <v>61.745</v>
       </c>
       <c r="I29" t="n">
-        <v>56.495</v>
+        <v>62.044</v>
       </c>
       <c r="J29" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K29" t="n">
-        <v>51.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
@@ -1559,21 +1559,21 @@
         <v>24</v>
       </c>
       <c r="B30" t="n">
-        <v>1443</v>
+        <v>6</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1583,20 +1583,20 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>56.695</v>
+        <v>62.094</v>
       </c>
       <c r="I30" t="n">
-        <v>57.195</v>
+        <v>62.444</v>
       </c>
       <c r="J30" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="K30" t="n">
-        <v>36</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="31">
@@ -1604,21 +1604,21 @@
         <v>25</v>
       </c>
       <c r="B31" t="n">
-        <v>1537</v>
+        <v>173</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1628,20 +1628,20 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>87.2%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>59.845</v>
+        <v>69.14400000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>60.295</v>
+        <v>69.64400000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="K31" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32">
@@ -1649,21 +1649,21 @@
         <v>26</v>
       </c>
       <c r="B32" t="n">
-        <v>1553</v>
+        <v>197</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1673,20 +1673,20 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>60.395</v>
+        <v>70.194</v>
       </c>
       <c r="I32" t="n">
-        <v>60.745</v>
+        <v>70.64400000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="K32" t="n">
-        <v>51.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="33">
@@ -1694,7 +1694,7 @@
         <v>27</v>
       </c>
       <c r="B33" t="n">
-        <v>1635</v>
+        <v>181</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -1718,20 +1718,20 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>81.1%</t>
+          <t>74.3%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>61.745</v>
+        <v>79.593</v>
       </c>
       <c r="I33" t="n">
-        <v>62.044</v>
+        <v>79.943</v>
       </c>
       <c r="J33" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="K33" t="n">
-        <v>60</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="34">
@@ -1739,7 +1739,7 @@
         <v>28</v>
       </c>
       <c r="B34" t="n">
-        <v>1632</v>
+        <v>338</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -1763,20 +1763,20 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>62.094</v>
+        <v>88.44199999999999</v>
       </c>
       <c r="I34" t="n">
-        <v>62.444</v>
+        <v>88.892</v>
       </c>
       <c r="J34" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="K34" t="n">
-        <v>51.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35">
@@ -1784,7 +1784,7 @@
         <v>29</v>
       </c>
       <c r="B35" t="n">
-        <v>800026</v>
+        <v>391</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -1808,20 +1808,20 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>63.4%</t>
+          <t>79.0%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>62.094</v>
+        <v>90.342</v>
       </c>
       <c r="I35" t="n">
-        <v>62.694</v>
+        <v>90.542</v>
       </c>
       <c r="J35" t="n">
-        <v>0.6</v>
+        <v>0.2</v>
       </c>
       <c r="K35" t="n">
-        <v>30</v>
+        <v>90</v>
       </c>
     </row>
     <row r="36">
@@ -1829,21 +1829,21 @@
         <v>30</v>
       </c>
       <c r="B36" t="n">
-        <v>1672</v>
+        <v>491</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1853,20 +1853,20 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="H36" t="n">
-        <v>63.244</v>
+        <v>95.19199999999999</v>
       </c>
       <c r="I36" t="n">
-        <v>63.644</v>
+        <v>95.791</v>
       </c>
       <c r="J36" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="K36" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="37">
@@ -1874,21 +1874,21 @@
         <v>31</v>
       </c>
       <c r="B37" t="n">
-        <v>1675</v>
+        <v>839</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1898,14 +1898,14 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>92.1%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>64.14400000000001</v>
+        <v>108.14</v>
       </c>
       <c r="I37" t="n">
-        <v>64.444</v>
+        <v>108.44</v>
       </c>
       <c r="J37" t="n">
         <v>0.3</v>
@@ -1919,7 +1919,7 @@
         <v>32</v>
       </c>
       <c r="B38" t="n">
-        <v>800029</v>
+        <v>979</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1943,20 +1943,20 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>81.5%</t>
         </is>
       </c>
       <c r="H38" t="n">
-        <v>67.194</v>
+        <v>112.29</v>
       </c>
       <c r="I38" t="n">
-        <v>68.39400000000001</v>
+        <v>112.64</v>
       </c>
       <c r="J38" t="n">
-        <v>1.2</v>
+        <v>0.35</v>
       </c>
       <c r="K38" t="n">
-        <v>15</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="39">
@@ -1964,21 +1964,21 @@
         <v>33</v>
       </c>
       <c r="B39" t="n">
-        <v>1782</v>
+        <v>1356</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1988,14 +1988,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>85.1%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>69.14400000000001</v>
+        <v>125.089</v>
       </c>
       <c r="I39" t="n">
-        <v>69.64400000000001</v>
+        <v>125.589</v>
       </c>
       <c r="J39" t="n">
         <v>0.5</v>
@@ -2009,21 +2009,21 @@
         <v>34</v>
       </c>
       <c r="B40" t="n">
-        <v>1824</v>
+        <v>1379</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2033,20 +2033,20 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>86.4%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>70.194</v>
+        <v>125.889</v>
       </c>
       <c r="I40" t="n">
-        <v>70.64400000000001</v>
+        <v>126.389</v>
       </c>
       <c r="J40" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="K40" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="41">
@@ -2054,7 +2054,7 @@
         <v>35</v>
       </c>
       <c r="B41" t="n">
-        <v>1881</v>
+        <v>1428</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -2078,20 +2078,20 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>72.694</v>
+        <v>127.139</v>
       </c>
       <c r="I41" t="n">
-        <v>73.09399999999999</v>
+        <v>127.589</v>
       </c>
       <c r="J41" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="K41" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="42">
@@ -2099,21 +2099,21 @@
         <v>36</v>
       </c>
       <c r="B42" t="n">
-        <v>2039</v>
+        <v>1558</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2123,20 +2123,20 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>79.593</v>
+        <v>131.138</v>
       </c>
       <c r="I42" t="n">
-        <v>79.943</v>
+        <v>131.438</v>
       </c>
       <c r="J42" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K42" t="n">
-        <v>51.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="43">
@@ -2144,21 +2144,21 @@
         <v>37</v>
       </c>
       <c r="B43" t="n">
-        <v>2045</v>
+        <v>1552</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2168,14 +2168,14 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>80.04300000000001</v>
+        <v>131.188</v>
       </c>
       <c r="I43" t="n">
-        <v>80.343</v>
+        <v>131.488</v>
       </c>
       <c r="J43" t="n">
         <v>0.3</v>
@@ -2189,21 +2189,21 @@
         <v>38</v>
       </c>
       <c r="B44" t="n">
-        <v>2205</v>
+        <v>1636</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2213,20 +2213,20 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>88.44199999999999</v>
+        <v>134.188</v>
       </c>
       <c r="I44" t="n">
-        <v>88.892</v>
+        <v>134.538</v>
       </c>
       <c r="J44" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="K44" t="n">
-        <v>40</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="45">
@@ -2234,21 +2234,21 @@
         <v>39</v>
       </c>
       <c r="B45" t="n">
-        <v>2287</v>
+        <v>1671</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2258,20 +2258,20 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>79.0%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>90.342</v>
+        <v>135.488</v>
       </c>
       <c r="I45" t="n">
-        <v>90.542</v>
+        <v>135.788</v>
       </c>
       <c r="J45" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="K45" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
     </row>
     <row r="46">
@@ -2279,7 +2279,7 @@
         <v>40</v>
       </c>
       <c r="B46" t="n">
-        <v>2407</v>
+        <v>1723</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2303,20 +2303,20 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>86.9%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>95.19199999999999</v>
+        <v>137.188</v>
       </c>
       <c r="I46" t="n">
-        <v>95.791</v>
+        <v>137.538</v>
       </c>
       <c r="J46" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="K46" t="n">
-        <v>30</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="47">
@@ -2324,7 +2324,7 @@
         <v>41</v>
       </c>
       <c r="B47" t="n">
-        <v>800038</v>
+        <v>1811</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2343,25 +2343,25 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>opposite</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>108.14</v>
+        <v>140.838</v>
       </c>
       <c r="I47" t="n">
-        <v>107.84</v>
+        <v>141.287</v>
       </c>
       <c r="J47" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="K47" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="48">
@@ -2369,21 +2369,21 @@
         <v>42</v>
       </c>
       <c r="B48" t="n">
-        <v>2761</v>
+        <v>1995</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2393,20 +2393,20 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>84.5%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>108.14</v>
+        <v>147.887</v>
       </c>
       <c r="I48" t="n">
-        <v>108.44</v>
+        <v>148.387</v>
       </c>
       <c r="J48" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="K48" t="n">
-        <v>60</v>
+        <v>36</v>
       </c>
     </row>
     <row r="49">
@@ -2414,44 +2414,44 @@
         <v>43</v>
       </c>
       <c r="B49" t="n">
-        <v>800039</v>
+        <v>2013</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>opposite</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>72.2%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>108.29</v>
+        <v>148.037</v>
       </c>
       <c r="I49" t="n">
-        <v>109.04</v>
+        <v>148.387</v>
       </c>
       <c r="J49" t="n">
-        <v>0.75</v>
+        <v>0.35</v>
       </c>
       <c r="K49" t="n">
-        <v>24</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="50">
@@ -2459,44 +2459,44 @@
         <v>44</v>
       </c>
       <c r="B50" t="n">
-        <v>800040</v>
+        <v>2200</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>opposite</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>111.74</v>
+        <v>153.736</v>
       </c>
       <c r="I50" t="n">
-        <v>109.79</v>
+        <v>154.086</v>
       </c>
       <c r="J50" t="n">
-        <v>1.95</v>
+        <v>0.35</v>
       </c>
       <c r="K50" t="n">
-        <v>9.199999999999999</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="51">
@@ -2504,21 +2504,21 @@
         <v>45</v>
       </c>
       <c r="B51" t="n">
-        <v>2904</v>
+        <v>2222</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2528,20 +2528,20 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>81.5%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>112.29</v>
+        <v>155.736</v>
       </c>
       <c r="I51" t="n">
-        <v>112.64</v>
+        <v>156.136</v>
       </c>
       <c r="J51" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="K51" t="n">
-        <v>51.4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="52">
@@ -2549,21 +2549,21 @@
         <v>46</v>
       </c>
       <c r="B52" t="n">
-        <v>3309</v>
+        <v>2323</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2573,20 +2573,20 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>85.1%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>125.089</v>
+        <v>158.636</v>
       </c>
       <c r="I52" t="n">
-        <v>125.589</v>
+        <v>158.936</v>
       </c>
       <c r="J52" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K52" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="53">
@@ -2594,21 +2594,21 @@
         <v>47</v>
       </c>
       <c r="B53" t="n">
-        <v>3346</v>
+        <v>2742</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2618,20 +2618,20 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>86.4%</t>
+          <t>91.7%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>125.889</v>
+        <v>174.785</v>
       </c>
       <c r="I53" t="n">
-        <v>126.389</v>
+        <v>175.584</v>
       </c>
       <c r="J53" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="K53" t="n">
-        <v>36</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="54">
@@ -2639,21 +2639,21 @@
         <v>48</v>
       </c>
       <c r="B54" t="n">
-        <v>3373</v>
+        <v>2812</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2663,20 +2663,20 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>86.5%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>127.139</v>
+        <v>176.484</v>
       </c>
       <c r="I54" t="n">
-        <v>127.589</v>
+        <v>176.834</v>
       </c>
       <c r="J54" t="n">
-        <v>0.45</v>
+        <v>0.35</v>
       </c>
       <c r="K54" t="n">
-        <v>40</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="55">
@@ -2684,7 +2684,7 @@
         <v>49</v>
       </c>
       <c r="B55" t="n">
-        <v>800045</v>
+        <v>2901</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -2708,20 +2708,20 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>127.639</v>
+        <v>178.634</v>
       </c>
       <c r="I55" t="n">
-        <v>127.189</v>
+        <v>179.034</v>
       </c>
       <c r="J55" t="n">
-        <v>0.45</v>
+        <v>0.4</v>
       </c>
       <c r="K55" t="n">
-        <v>40</v>
+        <v>45</v>
       </c>
     </row>
     <row r="56">
@@ -2729,44 +2729,44 @@
         <v>50</v>
       </c>
       <c r="B56" t="n">
-        <v>800047</v>
+        <v>2927</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>opposite</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>88.8%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>128.089</v>
+        <v>180.184</v>
       </c>
       <c r="I56" t="n">
-        <v>127.939</v>
+        <v>180.534</v>
       </c>
       <c r="J56" t="n">
-        <v>0.15</v>
+        <v>0.35</v>
       </c>
       <c r="K56" t="n">
-        <v>120.1</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="57">
@@ -2774,7 +2774,7 @@
         <v>51</v>
       </c>
       <c r="B57" t="n">
-        <v>3529</v>
+        <v>2978</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -2798,20 +2798,20 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>88.2%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>131.138</v>
+        <v>181.984</v>
       </c>
       <c r="I57" t="n">
-        <v>131.438</v>
+        <v>182.334</v>
       </c>
       <c r="J57" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="K57" t="n">
-        <v>60</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="58">
@@ -2819,21 +2819,21 @@
         <v>52</v>
       </c>
       <c r="B58" t="n">
-        <v>3522</v>
+        <v>3020</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2843,20 +2843,20 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>131.188</v>
+        <v>183.234</v>
       </c>
       <c r="I58" t="n">
-        <v>131.488</v>
+        <v>183.634</v>
       </c>
       <c r="J58" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K58" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="59">
@@ -2864,7 +2864,7 @@
         <v>53</v>
       </c>
       <c r="B59" t="n">
-        <v>3634</v>
+        <v>3098</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -2888,20 +2888,20 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="H59" t="n">
-        <v>134.188</v>
+        <v>185.633</v>
       </c>
       <c r="I59" t="n">
-        <v>134.538</v>
+        <v>186.184</v>
       </c>
       <c r="J59" t="n">
-        <v>0.35</v>
+        <v>0.55</v>
       </c>
       <c r="K59" t="n">
-        <v>51.4</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="60">
@@ -2909,7 +2909,7 @@
         <v>54</v>
       </c>
       <c r="B60" t="n">
-        <v>3680</v>
+        <v>3207</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2933,20 +2933,20 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="H60" t="n">
-        <v>135.488</v>
+        <v>189.933</v>
       </c>
       <c r="I60" t="n">
-        <v>135.788</v>
+        <v>190.333</v>
       </c>
       <c r="J60" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K60" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="61">
@@ -2954,7 +2954,7 @@
         <v>55</v>
       </c>
       <c r="B61" t="n">
-        <v>3736</v>
+        <v>3234</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -2978,20 +2978,20 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>86.9%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="H61" t="n">
-        <v>137.188</v>
+        <v>191.533</v>
       </c>
       <c r="I61" t="n">
-        <v>137.538</v>
+        <v>192.033</v>
       </c>
       <c r="J61" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="K61" t="n">
-        <v>51.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="62">
@@ -2999,7 +2999,7 @@
         <v>56</v>
       </c>
       <c r="B62" t="n">
-        <v>3834</v>
+        <v>3310</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -3023,20 +3023,20 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>83.2%</t>
         </is>
       </c>
       <c r="H62" t="n">
-        <v>140.838</v>
+        <v>194.683</v>
       </c>
       <c r="I62" t="n">
-        <v>141.287</v>
+        <v>195.483</v>
       </c>
       <c r="J62" t="n">
-        <v>0.45</v>
+        <v>0.8</v>
       </c>
       <c r="K62" t="n">
-        <v>40</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="63">
@@ -3044,44 +3044,44 @@
         <v>57</v>
       </c>
       <c r="B63" t="n">
-        <v>800055</v>
+        <v>3333</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>opposite</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H63" t="n">
-        <v>146.537</v>
+        <v>195.283</v>
       </c>
       <c r="I63" t="n">
-        <v>144.887</v>
+        <v>195.383</v>
       </c>
       <c r="J63" t="n">
-        <v>1.65</v>
+        <v>0.1</v>
       </c>
       <c r="K63" t="n">
-        <v>10.9</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64">
@@ -3089,7 +3089,7 @@
         <v>58</v>
       </c>
       <c r="B64" t="n">
-        <v>800056</v>
+        <v>3600</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -3113,20 +3113,20 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>74.6%</t>
         </is>
       </c>
       <c r="H64" t="n">
-        <v>146.987</v>
+        <v>204.532</v>
       </c>
       <c r="I64" t="n">
-        <v>146.087</v>
+        <v>204.882</v>
       </c>
       <c r="J64" t="n">
-        <v>0.9</v>
+        <v>0.35</v>
       </c>
       <c r="K64" t="n">
-        <v>20</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="65">
@@ -3134,7 +3134,7 @@
         <v>59</v>
       </c>
       <c r="B65" t="n">
-        <v>4029</v>
+        <v>3610</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -3158,20 +3158,20 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>84.5%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="H65" t="n">
-        <v>147.887</v>
+        <v>205.532</v>
       </c>
       <c r="I65" t="n">
-        <v>148.387</v>
+        <v>205.832</v>
       </c>
       <c r="J65" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K65" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="66">
@@ -3179,7 +3179,7 @@
         <v>60</v>
       </c>
       <c r="B66" t="n">
-        <v>4056</v>
+        <v>3889</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -3203,14 +3203,14 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>72.2%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="H66" t="n">
-        <v>148.037</v>
+        <v>212.881</v>
       </c>
       <c r="I66" t="n">
-        <v>148.387</v>
+        <v>213.231</v>
       </c>
       <c r="J66" t="n">
         <v>0.35</v>
@@ -3224,21 +3224,21 @@
         <v>61</v>
       </c>
       <c r="B67" t="n">
-        <v>800058</v>
+        <v>4047</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -3248,20 +3248,20 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="H67" t="n">
-        <v>149.387</v>
+        <v>217.381</v>
       </c>
       <c r="I67" t="n">
-        <v>151.337</v>
+        <v>217.731</v>
       </c>
       <c r="J67" t="n">
-        <v>1.95</v>
+        <v>0.35</v>
       </c>
       <c r="K67" t="n">
-        <v>9.199999999999999</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="68">
@@ -3269,21 +3269,21 @@
         <v>62</v>
       </c>
       <c r="B68" t="n">
-        <v>800059</v>
+        <v>4102</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -3293,20 +3293,20 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="H68" t="n">
-        <v>153.286</v>
+        <v>219.28</v>
       </c>
       <c r="I68" t="n">
-        <v>153.886</v>
+        <v>219.631</v>
       </c>
       <c r="J68" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="K68" t="n">
-        <v>30</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="69">
@@ -3314,7 +3314,7 @@
         <v>63</v>
       </c>
       <c r="B69" t="n">
-        <v>4263</v>
+        <v>4132</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -3338,20 +3338,20 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>86.2%</t>
         </is>
       </c>
       <c r="H69" t="n">
-        <v>153.736</v>
+        <v>220.48</v>
       </c>
       <c r="I69" t="n">
-        <v>154.086</v>
+        <v>220.88</v>
       </c>
       <c r="J69" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="K69" t="n">
-        <v>51.4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="70">
@@ -3359,21 +3359,21 @@
         <v>64</v>
       </c>
       <c r="B70" t="n">
-        <v>4285</v>
+        <v>4216</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3383,20 +3383,20 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>63.5%</t>
         </is>
       </c>
       <c r="H70" t="n">
-        <v>155.736</v>
+        <v>223.68</v>
       </c>
       <c r="I70" t="n">
-        <v>156.136</v>
+        <v>224.13</v>
       </c>
       <c r="J70" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="K70" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="71">
@@ -3404,7 +3404,7 @@
         <v>65</v>
       </c>
       <c r="B71" t="n">
-        <v>4435</v>
+        <v>4219</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -3428,14 +3428,14 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="H71" t="n">
-        <v>158.636</v>
+        <v>223.68</v>
       </c>
       <c r="I71" t="n">
-        <v>158.936</v>
+        <v>223.98</v>
       </c>
       <c r="J71" t="n">
         <v>0.3</v>
@@ -3449,7 +3449,7 @@
         <v>66</v>
       </c>
       <c r="B72" t="n">
-        <v>800060</v>
+        <v>4221</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -3473,20 +3473,20 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="H72" t="n">
-        <v>164.385</v>
+        <v>224.28</v>
       </c>
       <c r="I72" t="n">
-        <v>164.535</v>
+        <v>224.68</v>
       </c>
       <c r="J72" t="n">
-        <v>0.15</v>
+        <v>0.4</v>
       </c>
       <c r="K72" t="n">
-        <v>120</v>
+        <v>45</v>
       </c>
     </row>
     <row r="73">
@@ -3494,21 +3494,21 @@
         <v>67</v>
       </c>
       <c r="B73" t="n">
-        <v>4909</v>
+        <v>4303</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -3518,20 +3518,20 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>91.7%</t>
+          <t>85.2%</t>
         </is>
       </c>
       <c r="H73" t="n">
-        <v>174.785</v>
+        <v>227.48</v>
       </c>
       <c r="I73" t="n">
-        <v>175.584</v>
+        <v>228.03</v>
       </c>
       <c r="J73" t="n">
-        <v>0.8</v>
+        <v>0.55</v>
       </c>
       <c r="K73" t="n">
-        <v>22.5</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="74">
@@ -3539,21 +3539,21 @@
         <v>68</v>
       </c>
       <c r="B74" t="n">
-        <v>5005</v>
+        <v>4283</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3563,20 +3563,20 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>86.5%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="H74" t="n">
-        <v>176.484</v>
+        <v>227.63</v>
       </c>
       <c r="I74" t="n">
-        <v>176.834</v>
+        <v>228.08</v>
       </c>
       <c r="J74" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="K74" t="n">
-        <v>51.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="75">
@@ -3584,7 +3584,7 @@
         <v>69</v>
       </c>
       <c r="B75" t="n">
-        <v>800063</v>
+        <v>4804</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3608,20 +3608,20 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="H75" t="n">
-        <v>177.284</v>
+        <v>246.178</v>
       </c>
       <c r="I75" t="n">
-        <v>177.434</v>
+        <v>246.628</v>
       </c>
       <c r="J75" t="n">
-        <v>0.15</v>
+        <v>0.45</v>
       </c>
       <c r="K75" t="n">
-        <v>120</v>
+        <v>40</v>
       </c>
     </row>
     <row r="76">
@@ -3629,21 +3629,21 @@
         <v>70</v>
       </c>
       <c r="B76" t="n">
-        <v>5104</v>
+        <v>5063</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3653,20 +3653,20 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>81.3%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="H76" t="n">
-        <v>178.634</v>
+        <v>254.527</v>
       </c>
       <c r="I76" t="n">
-        <v>179.034</v>
+        <v>254.877</v>
       </c>
       <c r="J76" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="K76" t="n">
-        <v>45</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="77">
@@ -3674,21 +3674,21 @@
         <v>71</v>
       </c>
       <c r="B77" t="n">
-        <v>5135</v>
+        <v>5078</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3698,20 +3698,20 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>88.8%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="H77" t="n">
-        <v>180.184</v>
+        <v>255.327</v>
       </c>
       <c r="I77" t="n">
-        <v>180.534</v>
+        <v>255.827</v>
       </c>
       <c r="J77" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="K77" t="n">
-        <v>51.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="78">
@@ -3719,7 +3719,7 @@
         <v>72</v>
       </c>
       <c r="B78" t="n">
-        <v>5197</v>
+        <v>5276</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -3743,20 +3743,20 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>88.2%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="H78" t="n">
-        <v>181.984</v>
+        <v>260.977</v>
       </c>
       <c r="I78" t="n">
-        <v>182.334</v>
+        <v>261.477</v>
       </c>
       <c r="J78" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="K78" t="n">
-        <v>51.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="79">
@@ -3764,21 +3764,21 @@
         <v>73</v>
       </c>
       <c r="B79" t="n">
-        <v>5229</v>
+        <v>5386</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3788,20 +3788,20 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="H79" t="n">
-        <v>183.234</v>
+        <v>263.627</v>
       </c>
       <c r="I79" t="n">
-        <v>183.634</v>
+        <v>264.177</v>
       </c>
       <c r="J79" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="K79" t="n">
-        <v>45</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="80">
@@ -3809,21 +3809,21 @@
         <v>74</v>
       </c>
       <c r="B80" t="n">
-        <v>5359</v>
+        <v>5413</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3833,20 +3833,20 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="H80" t="n">
-        <v>185.633</v>
+        <v>264.227</v>
       </c>
       <c r="I80" t="n">
-        <v>186.184</v>
+        <v>264.577</v>
       </c>
       <c r="J80" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="K80" t="n">
-        <v>32.7</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="81">
@@ -3854,7 +3854,7 @@
         <v>75</v>
       </c>
       <c r="B81" t="n">
-        <v>800065</v>
+        <v>5718</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -3878,20 +3878,20 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>72.5%</t>
         </is>
       </c>
       <c r="H81" t="n">
-        <v>186.133</v>
+        <v>272.476</v>
       </c>
       <c r="I81" t="n">
-        <v>186.284</v>
+        <v>272.776</v>
       </c>
       <c r="J81" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="K81" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
     </row>
     <row r="82">
@@ -3899,7 +3899,7 @@
         <v>76</v>
       </c>
       <c r="B82" t="n">
-        <v>5479</v>
+        <v>5914</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -3923,20 +3923,20 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="H82" t="n">
-        <v>189.933</v>
+        <v>277.525</v>
       </c>
       <c r="I82" t="n">
-        <v>190.333</v>
+        <v>278.025</v>
       </c>
       <c r="J82" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K82" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="83">
@@ -3944,7 +3944,7 @@
         <v>77</v>
       </c>
       <c r="B83" t="n">
-        <v>5529</v>
+        <v>6123</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -3968,20 +3968,20 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="H83" t="n">
-        <v>191.533</v>
+        <v>283.425</v>
       </c>
       <c r="I83" t="n">
-        <v>192.033</v>
+        <v>283.825</v>
       </c>
       <c r="J83" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
       <c r="K83" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="84">
@@ -3989,7 +3989,7 @@
         <v>78</v>
       </c>
       <c r="B84" t="n">
-        <v>5645</v>
+        <v>6240</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -4013,20 +4013,20 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>83.2%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="H84" t="n">
-        <v>194.683</v>
+        <v>285.525</v>
       </c>
       <c r="I84" t="n">
-        <v>195.483</v>
+        <v>285.775</v>
       </c>
       <c r="J84" t="n">
-        <v>0.8</v>
+        <v>0.25</v>
       </c>
       <c r="K84" t="n">
-        <v>22.5</v>
+        <v>72</v>
       </c>
     </row>
     <row r="85">
@@ -4034,21 +4034,21 @@
         <v>79</v>
       </c>
       <c r="B85" t="n">
-        <v>5682</v>
+        <v>6500</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -4058,20 +4058,20 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>85.6%</t>
         </is>
       </c>
       <c r="H85" t="n">
-        <v>195.283</v>
+        <v>293.074</v>
       </c>
       <c r="I85" t="n">
-        <v>195.383</v>
+        <v>293.574</v>
       </c>
       <c r="J85" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="K85" t="n">
-        <v>180</v>
+        <v>36</v>
       </c>
     </row>
     <row r="86">
@@ -4079,21 +4079,21 @@
         <v>80</v>
       </c>
       <c r="B86" t="n">
-        <v>5956</v>
+        <v>6647</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -4103,14 +4103,14 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>74.6%</t>
+          <t>76.8%</t>
         </is>
       </c>
       <c r="H86" t="n">
-        <v>204.532</v>
+        <v>296.774</v>
       </c>
       <c r="I86" t="n">
-        <v>204.882</v>
+        <v>297.124</v>
       </c>
       <c r="J86" t="n">
         <v>0.35</v>
@@ -4124,21 +4124,21 @@
         <v>81</v>
       </c>
       <c r="B87" t="n">
-        <v>5962</v>
+        <v>6675</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -4148,20 +4148,20 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="H87" t="n">
-        <v>205.532</v>
+        <v>297.824</v>
       </c>
       <c r="I87" t="n">
-        <v>205.832</v>
+        <v>298.174</v>
       </c>
       <c r="J87" t="n">
-        <v>0.3</v>
+        <v>0.35</v>
       </c>
       <c r="K87" t="n">
-        <v>60</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="88">
@@ -4169,21 +4169,21 @@
         <v>82</v>
       </c>
       <c r="B88" t="n">
-        <v>6165</v>
+        <v>6924</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -4193,20 +4193,20 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>84.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="H88" t="n">
-        <v>212.881</v>
+        <v>305.023</v>
       </c>
       <c r="I88" t="n">
-        <v>213.231</v>
+        <v>305.473</v>
       </c>
       <c r="J88" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="K88" t="n">
-        <v>51.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="89">
@@ -4214,7 +4214,7 @@
         <v>83</v>
       </c>
       <c r="B89" t="n">
-        <v>6291</v>
+        <v>7171</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -4238,20 +4238,20 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="H89" t="n">
-        <v>217.381</v>
+        <v>312.322</v>
       </c>
       <c r="I89" t="n">
-        <v>217.731</v>
+        <v>312.822</v>
       </c>
       <c r="J89" t="n">
-        <v>0.35</v>
+        <v>0.5</v>
       </c>
       <c r="K89" t="n">
-        <v>51.4</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90">
@@ -4259,21 +4259,21 @@
         <v>84</v>
       </c>
       <c r="B90" t="n">
-        <v>6357</v>
+        <v>7197</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Pickup / Micro Truck</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Pickup / micro truck / delivery</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -4283,20 +4283,20 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>84.1%</t>
         </is>
       </c>
       <c r="H90" t="n">
-        <v>219.28</v>
+        <v>312.772</v>
       </c>
       <c r="I90" t="n">
-        <v>219.631</v>
+        <v>313.222</v>
       </c>
       <c r="J90" t="n">
-        <v>0.35</v>
+        <v>0.45</v>
       </c>
       <c r="K90" t="n">
-        <v>51.4</v>
+        <v>40</v>
       </c>
     </row>
     <row r="91">
@@ -4304,7 +4304,7 @@
         <v>85</v>
       </c>
       <c r="B91" t="n">
-        <v>6407</v>
+        <v>7233</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -4328,14 +4328,14 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>86.2%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="H91" t="n">
-        <v>220.48</v>
+        <v>314.022</v>
       </c>
       <c r="I91" t="n">
-        <v>220.88</v>
+        <v>314.422</v>
       </c>
       <c r="J91" t="n">
         <v>0.4</v>
@@ -4349,21 +4349,21 @@
         <v>86</v>
       </c>
       <c r="B92" t="n">
-        <v>6496</v>
+        <v>7313</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4373,14 +4373,14 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>63.5%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="H92" t="n">
-        <v>223.68</v>
+        <v>315.372</v>
       </c>
       <c r="I92" t="n">
-        <v>224.13</v>
+        <v>315.822</v>
       </c>
       <c r="J92" t="n">
         <v>0.45</v>
@@ -4394,21 +4394,21 @@
         <v>87</v>
       </c>
       <c r="B93" t="n">
-        <v>6499</v>
+        <v>7332</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -4418,20 +4418,20 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>41.6%</t>
         </is>
       </c>
       <c r="H93" t="n">
-        <v>223.68</v>
+        <v>315.372</v>
       </c>
       <c r="I93" t="n">
-        <v>223.98</v>
+        <v>315.822</v>
       </c>
       <c r="J93" t="n">
-        <v>0.3</v>
+        <v>0.45</v>
       </c>
       <c r="K93" t="n">
-        <v>60</v>
+        <v>40</v>
       </c>
     </row>
     <row r="94">
@@ -4439,7 +4439,7 @@
         <v>88</v>
       </c>
       <c r="B94" t="n">
-        <v>6500</v>
+        <v>7499</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -4463,20 +4463,20 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>86.0%</t>
         </is>
       </c>
       <c r="H94" t="n">
-        <v>224.28</v>
+        <v>319.422</v>
       </c>
       <c r="I94" t="n">
-        <v>224.68</v>
+        <v>319.772</v>
       </c>
       <c r="J94" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="K94" t="n">
-        <v>45</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="95">
@@ -4484,7 +4484,7 @@
         <v>89</v>
       </c>
       <c r="B95" t="n">
-        <v>6649</v>
+        <v>7516</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -4508,20 +4508,20 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>82.7%</t>
         </is>
       </c>
       <c r="H95" t="n">
-        <v>227.48</v>
+        <v>320.322</v>
       </c>
       <c r="I95" t="n">
-        <v>228.03</v>
+        <v>320.672</v>
       </c>
       <c r="J95" t="n">
-        <v>0.55</v>
+        <v>0.35</v>
       </c>
       <c r="K95" t="n">
-        <v>32.7</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="96">
@@ -4529,7 +4529,7 @@
         <v>90</v>
       </c>
       <c r="B96" t="n">
-        <v>6621</v>
+        <v>8041</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -4553,20 +4553,20 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>78.5%</t>
         </is>
       </c>
       <c r="H96" t="n">
-        <v>227.63</v>
+        <v>335.07</v>
       </c>
       <c r="I96" t="n">
-        <v>228.08</v>
+        <v>335.67</v>
       </c>
       <c r="J96" t="n">
-        <v>0.45</v>
+        <v>0.6</v>
       </c>
       <c r="K96" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
     </row>
     <row r="97">
@@ -4574,7 +4574,7 @@
         <v>91</v>
       </c>
       <c r="B97" t="n">
-        <v>800082</v>
+        <v>8141</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -4598,20 +4598,20 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>87.5%</t>
         </is>
       </c>
       <c r="H97" t="n">
-        <v>245.078</v>
+        <v>337.87</v>
       </c>
       <c r="I97" t="n">
-        <v>245.678</v>
+        <v>338.52</v>
       </c>
       <c r="J97" t="n">
-        <v>0.6</v>
+        <v>0.65</v>
       </c>
       <c r="K97" t="n">
-        <v>30</v>
+        <v>27.7</v>
       </c>
     </row>
     <row r="98">
@@ -4619,7 +4619,7 @@
         <v>92</v>
       </c>
       <c r="B98" t="n">
-        <v>7238</v>
+        <v>8256</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -4643,20 +4643,20 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="H98" t="n">
-        <v>246.178</v>
+        <v>340.32</v>
       </c>
       <c r="I98" t="n">
-        <v>246.628</v>
+        <v>340.82</v>
       </c>
       <c r="J98" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="K98" t="n">
-        <v>40</v>
+        <v>36</v>
       </c>
     </row>
     <row r="99">
@@ -4664,21 +4664,21 @@
         <v>93</v>
       </c>
       <c r="B99" t="n">
-        <v>7486</v>
+        <v>8438</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4688,20 +4688,20 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>83.3%</t>
         </is>
       </c>
       <c r="H99" t="n">
-        <v>254.527</v>
+        <v>346.219</v>
       </c>
       <c r="I99" t="n">
-        <v>254.877</v>
+        <v>346.519</v>
       </c>
       <c r="J99" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K99" t="n">
-        <v>51.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="100">
@@ -4709,21 +4709,21 @@
         <v>94</v>
       </c>
       <c r="B100" t="n">
-        <v>7502</v>
+        <v>8477</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4733,20 +4733,20 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>81.4%</t>
+          <t>92.4%</t>
         </is>
       </c>
       <c r="H100" t="n">
-        <v>255.327</v>
+        <v>348.669</v>
       </c>
       <c r="I100" t="n">
-        <v>255.827</v>
+        <v>348.969</v>
       </c>
       <c r="J100" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K100" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="101">
@@ -4754,21 +4754,21 @@
         <v>95</v>
       </c>
       <c r="B101" t="n">
-        <v>7665</v>
+        <v>8526</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4778,20 +4778,20 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>76.9%</t>
+          <t>78.0%</t>
         </is>
       </c>
       <c r="H101" t="n">
-        <v>260.977</v>
+        <v>349.669</v>
       </c>
       <c r="I101" t="n">
-        <v>261.477</v>
+        <v>350.119</v>
       </c>
       <c r="J101" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="K101" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="102">
@@ -4799,21 +4799,21 @@
         <v>96</v>
       </c>
       <c r="B102" t="n">
-        <v>800087</v>
+        <v>8597</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4823,20 +4823,20 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>65.7%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="H102" t="n">
-        <v>262.177</v>
+        <v>351.569</v>
       </c>
       <c r="I102" t="n">
-        <v>260.977</v>
+        <v>351.869</v>
       </c>
       <c r="J102" t="n">
-        <v>1.2</v>
+        <v>0.3</v>
       </c>
       <c r="K102" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
     </row>
     <row r="103">
@@ -4844,21 +4844,21 @@
         <v>97</v>
       </c>
       <c r="B103" t="n">
-        <v>7764</v>
+        <v>8623</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>2-Axle Truck (Jumbo)</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>2-Axle Truck</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4868,20 +4868,20 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="H103" t="n">
-        <v>263.627</v>
+        <v>352.519</v>
       </c>
       <c r="I103" t="n">
-        <v>264.177</v>
+        <v>352.919</v>
       </c>
       <c r="J103" t="n">
-        <v>0.55</v>
+        <v>0.4</v>
       </c>
       <c r="K103" t="n">
-        <v>32.7</v>
+        <v>45</v>
       </c>
     </row>
     <row r="104">
@@ -4889,7 +4889,7 @@
         <v>98</v>
       </c>
       <c r="B104" t="n">
-        <v>7784</v>
+        <v>8668</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -4913,20 +4913,20 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>91.6%</t>
         </is>
       </c>
       <c r="H104" t="n">
-        <v>264.227</v>
+        <v>353.869</v>
       </c>
       <c r="I104" t="n">
-        <v>264.577</v>
+        <v>354.169</v>
       </c>
       <c r="J104" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K104" t="n">
-        <v>51.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="105">
@@ -4934,7 +4934,7 @@
         <v>99</v>
       </c>
       <c r="B105" t="n">
-        <v>8039</v>
+        <v>8713</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -4958,20 +4958,20 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>72.5%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="H105" t="n">
-        <v>272.476</v>
+        <v>355.269</v>
       </c>
       <c r="I105" t="n">
-        <v>272.776</v>
+        <v>355.868</v>
       </c>
       <c r="J105" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="K105" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
     </row>
     <row r="106">
@@ -4979,44 +4979,44 @@
         <v>100</v>
       </c>
       <c r="B106" t="n">
-        <v>800091</v>
+        <v>8724</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>normal</t>
+          <t>opposite</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="H106" t="n">
-        <v>277.475</v>
+        <v>355.318</v>
       </c>
       <c r="I106" t="n">
-        <v>277.025</v>
+        <v>355.618</v>
       </c>
       <c r="J106" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="K106" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="107">
@@ -5024,21 +5024,21 @@
         <v>101</v>
       </c>
       <c r="B107" t="n">
-        <v>8194</v>
+        <v>8830</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -5048,20 +5048,20 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="H107" t="n">
-        <v>277.525</v>
+        <v>357.318</v>
       </c>
       <c r="I107" t="n">
-        <v>278.025</v>
+        <v>357.668</v>
       </c>
       <c r="J107" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="K107" t="n">
-        <v>36</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="108">
@@ -5069,7 +5069,7 @@
         <v>102</v>
       </c>
       <c r="B108" t="n">
-        <v>8357</v>
+        <v>9105</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -5093,20 +5093,20 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="H108" t="n">
-        <v>283.425</v>
+        <v>367.267</v>
       </c>
       <c r="I108" t="n">
-        <v>283.825</v>
+        <v>367.617</v>
       </c>
       <c r="J108" t="n">
-        <v>0.4</v>
+        <v>0.35</v>
       </c>
       <c r="K108" t="n">
-        <v>45</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="109">
@@ -5114,7 +5114,7 @@
         <v>103</v>
       </c>
       <c r="B109" t="n">
-        <v>8408</v>
+        <v>9231</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -5138,20 +5138,20 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>83.9%</t>
+          <t>82.2%</t>
         </is>
       </c>
       <c r="H109" t="n">
-        <v>285.525</v>
+        <v>370.717</v>
       </c>
       <c r="I109" t="n">
-        <v>285.775</v>
+        <v>371.067</v>
       </c>
       <c r="J109" t="n">
-        <v>0.25</v>
+        <v>0.35</v>
       </c>
       <c r="K109" t="n">
-        <v>72</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="110">
@@ -5159,21 +5159,21 @@
         <v>104</v>
       </c>
       <c r="B110" t="n">
-        <v>8606</v>
+        <v>9286</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5183,20 +5183,20 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>85.6%</t>
+          <t>71.0%</t>
         </is>
       </c>
       <c r="H110" t="n">
-        <v>293.074</v>
+        <v>372.467</v>
       </c>
       <c r="I110" t="n">
-        <v>293.574</v>
+        <v>372.717</v>
       </c>
       <c r="J110" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="K110" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
     </row>
     <row r="111">
@@ -5204,21 +5204,21 @@
         <v>105</v>
       </c>
       <c r="B111" t="n">
-        <v>8753</v>
+        <v>9411</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -5228,20 +5228,20 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>76.8%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="H111" t="n">
-        <v>296.774</v>
+        <v>374.267</v>
       </c>
       <c r="I111" t="n">
-        <v>297.124</v>
+        <v>374.667</v>
       </c>
       <c r="J111" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="K111" t="n">
-        <v>51.4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="112">
@@ -5249,7 +5249,7 @@
         <v>106</v>
       </c>
       <c r="B112" t="n">
-        <v>8777</v>
+        <v>9549</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -5273,20 +5273,20 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>92.2%</t>
         </is>
       </c>
       <c r="H112" t="n">
-        <v>297.824</v>
+        <v>378.916</v>
       </c>
       <c r="I112" t="n">
-        <v>298.174</v>
+        <v>379.316</v>
       </c>
       <c r="J112" t="n">
-        <v>0.35</v>
+        <v>0.4</v>
       </c>
       <c r="K112" t="n">
-        <v>51.4</v>
+        <v>45</v>
       </c>
     </row>
     <row r="113">
@@ -5294,21 +5294,21 @@
         <v>107</v>
       </c>
       <c r="B113" t="n">
-        <v>9026</v>
+        <v>9797</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -5318,20 +5318,20 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="H113" t="n">
-        <v>305.023</v>
+        <v>384.866</v>
       </c>
       <c r="I113" t="n">
-        <v>305.473</v>
+        <v>385.416</v>
       </c>
       <c r="J113" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="K113" t="n">
-        <v>40</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="114">
@@ -5339,7 +5339,7 @@
         <v>108</v>
       </c>
       <c r="B114" t="n">
-        <v>9223</v>
+        <v>9853</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -5363,20 +5363,20 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>84.0%</t>
         </is>
       </c>
       <c r="H114" t="n">
-        <v>312.322</v>
+        <v>386.016</v>
       </c>
       <c r="I114" t="n">
-        <v>312.822</v>
+        <v>386.316</v>
       </c>
       <c r="J114" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="K114" t="n">
-        <v>36</v>
+        <v>60</v>
       </c>
     </row>
     <row r="115">
@@ -5384,21 +5384,21 @@
         <v>109</v>
       </c>
       <c r="B115" t="n">
-        <v>9250</v>
+        <v>9860</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Pickup / Micro Truck</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Pickup / micro truck / delivery</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -5408,20 +5408,20 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>84.1%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="H115" t="n">
-        <v>312.772</v>
+        <v>386.766</v>
       </c>
       <c r="I115" t="n">
-        <v>313.222</v>
+        <v>387.316</v>
       </c>
       <c r="J115" t="n">
-        <v>0.45</v>
+        <v>0.55</v>
       </c>
       <c r="K115" t="n">
-        <v>40</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="116">
@@ -5429,7 +5429,7 @@
         <v>110</v>
       </c>
       <c r="B116" t="n">
-        <v>9299</v>
+        <v>9903</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -5453,20 +5453,20 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="H116" t="n">
-        <v>314.022</v>
+        <v>388.066</v>
       </c>
       <c r="I116" t="n">
-        <v>314.422</v>
+        <v>388.565</v>
       </c>
       <c r="J116" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="K116" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
     </row>
     <row r="117">
@@ -5474,7 +5474,7 @@
         <v>111</v>
       </c>
       <c r="B117" t="n">
-        <v>9358</v>
+        <v>9951</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -5498,20 +5498,20 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>87.8%</t>
         </is>
       </c>
       <c r="H117" t="n">
-        <v>315.372</v>
+        <v>388.916</v>
       </c>
       <c r="I117" t="n">
-        <v>315.822</v>
+        <v>389.216</v>
       </c>
       <c r="J117" t="n">
-        <v>0.45</v>
+        <v>0.3</v>
       </c>
       <c r="K117" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
     </row>
     <row r="118">
@@ -5519,21 +5519,21 @@
         <v>112</v>
       </c>
       <c r="B118" t="n">
-        <v>9385</v>
+        <v>10027</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -5543,20 +5543,20 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>41.6%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="H118" t="n">
-        <v>315.372</v>
+        <v>390.365</v>
       </c>
       <c r="I118" t="n">
-        <v>315.822</v>
+        <v>390.615</v>
       </c>
       <c r="J118" t="n">
-        <v>0.45</v>
+        <v>0.25</v>
       </c>
       <c r="K118" t="n">
-        <v>40</v>
+        <v>72</v>
       </c>
     </row>
     <row r="119">
@@ -5564,21 +5564,21 @@
         <v>113</v>
       </c>
       <c r="B119" t="n">
-        <v>800106</v>
+        <v>10041</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5588,20 +5588,20 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>30.0%</t>
+          <t>83.9%</t>
         </is>
       </c>
       <c r="H119" t="n">
-        <v>319.172</v>
+        <v>391.115</v>
       </c>
       <c r="I119" t="n">
-        <v>316.622</v>
+        <v>391.615</v>
       </c>
       <c r="J119" t="n">
-        <v>2.55</v>
+        <v>0.5</v>
       </c>
       <c r="K119" t="n">
-        <v>7.1</v>
+        <v>36</v>
       </c>
     </row>
     <row r="120">
@@ -5609,7 +5609,7 @@
         <v>114</v>
       </c>
       <c r="B120" t="n">
-        <v>9595</v>
+        <v>10184</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -5633,20 +5633,20 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>86.0%</t>
+          <t>83.5%</t>
         </is>
       </c>
       <c r="H120" t="n">
-        <v>319.422</v>
+        <v>395.215</v>
       </c>
       <c r="I120" t="n">
-        <v>319.772</v>
+        <v>395.515</v>
       </c>
       <c r="J120" t="n">
-        <v>0.35</v>
+        <v>0.3</v>
       </c>
       <c r="K120" t="n">
-        <v>51.4</v>
+        <v>60</v>
       </c>
     </row>
     <row r="121">
@@ -5654,21 +5654,21 @@
         <v>115</v>
       </c>
       <c r="B121" t="n">
-        <v>9606</v>
+        <v>10228</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -5678,14 +5678,14 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>82.7%</t>
+          <t>92.5%</t>
         </is>
       </c>
       <c r="H121" t="n">
-        <v>320.322</v>
+        <v>396.665</v>
       </c>
       <c r="I121" t="n">
-        <v>320.672</v>
+        <v>397.015</v>
       </c>
       <c r="J121" t="n">
         <v>0.35</v>
@@ -5699,21 +5699,21 @@
         <v>116</v>
       </c>
       <c r="B122" t="n">
-        <v>800110</v>
+        <v>10518</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Public Transportation (Angkot)</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Medium passenger vehicle</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -5723,20 +5723,20 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>19.7%</t>
+          <t>92.6%</t>
         </is>
       </c>
       <c r="H122" t="n">
-        <v>333.12</v>
+        <v>404.964</v>
       </c>
       <c r="I122" t="n">
-        <v>333.42</v>
+        <v>405.364</v>
       </c>
       <c r="J122" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="K122" t="n">
-        <v>60</v>
+        <v>45</v>
       </c>
     </row>
     <row r="123">
@@ -5744,21 +5744,21 @@
         <v>117</v>
       </c>
       <c r="B123" t="n">
-        <v>10037</v>
+        <v>10613</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -5768,20 +5768,20 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>78.5%</t>
+          <t>83.8%</t>
         </is>
       </c>
       <c r="H123" t="n">
-        <v>335.07</v>
+        <v>406.914</v>
       </c>
       <c r="I123" t="n">
-        <v>335.67</v>
+        <v>407.264</v>
       </c>
       <c r="J123" t="n">
-        <v>0.6</v>
+        <v>0.35</v>
       </c>
       <c r="K123" t="n">
-        <v>30</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="124">
@@ -5789,21 +5789,21 @@
         <v>118</v>
       </c>
       <c r="B124" t="n">
-        <v>10164</v>
+        <v>11020</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -5813,20 +5813,20 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="H124" t="n">
-        <v>337.87</v>
+        <v>420.813</v>
       </c>
       <c r="I124" t="n">
-        <v>338.52</v>
+        <v>421.313</v>
       </c>
       <c r="J124" t="n">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="K124" t="n">
-        <v>27.7</v>
+        <v>36</v>
       </c>
     </row>
     <row r="125">
@@ -5834,21 +5834,21 @@
         <v>119</v>
       </c>
       <c r="B125" t="n">
-        <v>10260</v>
+        <v>11258</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Motorcycle</t>
+          <t>Car / Sedan</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
+          <t>Sedan / jeep / station wagon</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -5858,20 +5858,20 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>88.3%</t>
         </is>
       </c>
       <c r="H125" t="n">
-        <v>340.32</v>
+        <v>428.712</v>
       </c>
       <c r="I125" t="n">
-        <v>340.82</v>
+        <v>429.062</v>
       </c>
       <c r="J125" t="n">
-        <v>0.5</v>
+        <v>0.35</v>
       </c>
       <c r="K125" t="n">
-        <v>36</v>
+        <v>51.4</v>
       </c>
     </row>
     <row r="126">
@@ -5879,7 +5879,7 @@
         <v>120</v>
       </c>
       <c r="B126" t="n">
-        <v>800113</v>
+        <v>11305</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -5903,20 +5903,20 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>30.4%</t>
+          <t>86.3%</t>
         </is>
       </c>
       <c r="H126" t="n">
-        <v>343.17</v>
+        <v>430.162</v>
       </c>
       <c r="I126" t="n">
-        <v>343.32</v>
+        <v>430.462</v>
       </c>
       <c r="J126" t="n">
-        <v>0.15</v>
+        <v>0.3</v>
       </c>
       <c r="K126" t="n">
-        <v>120.1</v>
+        <v>60</v>
       </c>
     </row>
     <row r="127">
@@ -5924,21 +5924,21 @@
         <v>121</v>
       </c>
       <c r="B127" t="n">
-        <v>10474</v>
+        <v>11677</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Car / Sedan</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sedan / jeep / station wagon</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -5948,20 +5948,20 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>87.2%</t>
         </is>
       </c>
       <c r="H127" t="n">
-        <v>346.219</v>
+        <v>441.411</v>
       </c>
       <c r="I127" t="n">
-        <v>346.519</v>
+        <v>441.961</v>
       </c>
       <c r="J127" t="n">
-        <v>0.3</v>
+        <v>0.55</v>
       </c>
       <c r="K127" t="n">
-        <v>60</v>
+        <v>32.7</v>
       </c>
     </row>
     <row r="128">
@@ -5969,21 +5969,21 @@
         <v>122</v>
       </c>
       <c r="B128" t="n">
-        <v>10552</v>
+        <v>11979</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Public Transportation (Angkot)</t>
+          <t>Motorcycle</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Medium passenger vehicle</t>
+          <t>Motorcycle / 3-wheel vehicle</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -5993,1504 +5993,19 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>92.4%</t>
+          <t>86.7%</t>
         </is>
       </c>
       <c r="H128" t="n">
-        <v>348.669</v>
+        <v>448.61</v>
       </c>
       <c r="I128" t="n">
-        <v>348.969</v>
+        <v>448.81</v>
       </c>
       <c r="J128" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="K128" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="n">
-        <v>123</v>
-      </c>
-      <c r="B129" t="n">
-        <v>10610</v>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>78.0%</t>
-        </is>
-      </c>
-      <c r="H129" t="n">
-        <v>349.669</v>
-      </c>
-      <c r="I129" t="n">
-        <v>350.119</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K129" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="n">
-        <v>124</v>
-      </c>
-      <c r="B130" t="n">
-        <v>10644</v>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>63.9%</t>
-        </is>
-      </c>
-      <c r="H130" t="n">
-        <v>351.569</v>
-      </c>
-      <c r="I130" t="n">
-        <v>351.869</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K130" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="n">
-        <v>125</v>
-      </c>
-      <c r="B131" t="n">
-        <v>800115</v>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>27.8%</t>
-        </is>
-      </c>
-      <c r="H131" t="n">
-        <v>354.119</v>
-      </c>
-      <c r="I131" t="n">
-        <v>352.019</v>
-      </c>
-      <c r="J131" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="K131" t="n">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="n">
-        <v>126</v>
-      </c>
-      <c r="B132" t="n">
-        <v>10664</v>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>2-Axle Truck (Jumbo)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>2-Axle Truck</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>87.8%</t>
-        </is>
-      </c>
-      <c r="H132" t="n">
-        <v>352.519</v>
-      </c>
-      <c r="I132" t="n">
-        <v>352.919</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K132" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="n">
-        <v>127</v>
-      </c>
-      <c r="B133" t="n">
-        <v>10707</v>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>91.6%</t>
-        </is>
-      </c>
-      <c r="H133" t="n">
-        <v>353.869</v>
-      </c>
-      <c r="I133" t="n">
-        <v>354.169</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K133" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="n">
-        <v>128</v>
-      </c>
-      <c r="B134" t="n">
-        <v>10752</v>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>82.9%</t>
-        </is>
-      </c>
-      <c r="H134" t="n">
-        <v>355.269</v>
-      </c>
-      <c r="I134" t="n">
-        <v>355.868</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K134" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="n">
-        <v>129</v>
-      </c>
-      <c r="B135" t="n">
-        <v>10773</v>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>52.1%</t>
-        </is>
-      </c>
-      <c r="H135" t="n">
-        <v>355.318</v>
-      </c>
-      <c r="I135" t="n">
-        <v>355.618</v>
-      </c>
-      <c r="J135" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K135" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="n">
-        <v>130</v>
-      </c>
-      <c r="B136" t="n">
-        <v>10882</v>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>67.0%</t>
-        </is>
-      </c>
-      <c r="H136" t="n">
-        <v>357.318</v>
-      </c>
-      <c r="I136" t="n">
-        <v>357.668</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K136" t="n">
-        <v>51.4</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="n">
-        <v>131</v>
-      </c>
-      <c r="B137" t="n">
-        <v>800119</v>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>normal</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>15.6%</t>
-        </is>
-      </c>
-      <c r="H137" t="n">
-        <v>358.018</v>
-      </c>
-      <c r="I137" t="n">
-        <v>357.868</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="K137" t="n">
-        <v>120.1</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="n">
-        <v>132</v>
-      </c>
-      <c r="B138" t="n">
-        <v>11158</v>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>52.0%</t>
-        </is>
-      </c>
-      <c r="H138" t="n">
-        <v>367.267</v>
-      </c>
-      <c r="I138" t="n">
-        <v>367.617</v>
-      </c>
-      <c r="J138" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K138" t="n">
-        <v>51.4</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="n">
-        <v>133</v>
-      </c>
-      <c r="B139" t="n">
-        <v>11283</v>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>82.2%</t>
-        </is>
-      </c>
-      <c r="H139" t="n">
-        <v>370.717</v>
-      </c>
-      <c r="I139" t="n">
-        <v>371.067</v>
-      </c>
-      <c r="J139" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K139" t="n">
-        <v>51.4</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="n">
-        <v>134</v>
-      </c>
-      <c r="B140" t="n">
-        <v>11348</v>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>71.0%</t>
-        </is>
-      </c>
-      <c r="H140" t="n">
-        <v>372.467</v>
-      </c>
-      <c r="I140" t="n">
-        <v>372.717</v>
-      </c>
-      <c r="J140" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K140" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="n">
-        <v>135</v>
-      </c>
-      <c r="B141" t="n">
-        <v>11443</v>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>70.6%</t>
-        </is>
-      </c>
-      <c r="H141" t="n">
-        <v>374.267</v>
-      </c>
-      <c r="I141" t="n">
-        <v>374.667</v>
-      </c>
-      <c r="J141" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K141" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="n">
-        <v>136</v>
-      </c>
-      <c r="B142" t="n">
-        <v>11559</v>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>92.2%</t>
-        </is>
-      </c>
-      <c r="H142" t="n">
-        <v>378.916</v>
-      </c>
-      <c r="I142" t="n">
-        <v>379.316</v>
-      </c>
-      <c r="J142" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K142" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="n">
-        <v>137</v>
-      </c>
-      <c r="B143" t="n">
-        <v>11790</v>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>53.9%</t>
-        </is>
-      </c>
-      <c r="H143" t="n">
-        <v>384.866</v>
-      </c>
-      <c r="I143" t="n">
-        <v>385.416</v>
-      </c>
-      <c r="J143" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K143" t="n">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="n">
-        <v>138</v>
-      </c>
-      <c r="B144" t="n">
-        <v>11836</v>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>Public Transportation (Angkot)</t>
-        </is>
-      </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>Medium passenger vehicle</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>84.0%</t>
-        </is>
-      </c>
-      <c r="H144" t="n">
-        <v>386.016</v>
-      </c>
-      <c r="I144" t="n">
-        <v>386.316</v>
-      </c>
-      <c r="J144" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K144" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="n">
-        <v>139</v>
-      </c>
-      <c r="B145" t="n">
-        <v>11846</v>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>82.8%</t>
-        </is>
-      </c>
-      <c r="H145" t="n">
-        <v>386.766</v>
-      </c>
-      <c r="I145" t="n">
-        <v>387.316</v>
-      </c>
-      <c r="J145" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K145" t="n">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="n">
-        <v>140</v>
-      </c>
-      <c r="B146" t="n">
-        <v>11918</v>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>73.6%</t>
-        </is>
-      </c>
-      <c r="H146" t="n">
-        <v>388.066</v>
-      </c>
-      <c r="I146" t="n">
-        <v>388.565</v>
-      </c>
-      <c r="J146" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K146" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="n">
-        <v>141</v>
-      </c>
-      <c r="B147" t="n">
-        <v>11983</v>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>87.8%</t>
-        </is>
-      </c>
-      <c r="H147" t="n">
-        <v>388.916</v>
-      </c>
-      <c r="I147" t="n">
-        <v>389.216</v>
-      </c>
-      <c r="J147" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K147" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="n">
-        <v>142</v>
-      </c>
-      <c r="B148" t="n">
-        <v>12033</v>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>89.6%</t>
-        </is>
-      </c>
-      <c r="H148" t="n">
-        <v>390.365</v>
-      </c>
-      <c r="I148" t="n">
-        <v>390.615</v>
-      </c>
-      <c r="J148" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="K148" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="n">
-        <v>143</v>
-      </c>
-      <c r="B149" t="n">
-        <v>12049</v>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>83.9%</t>
-        </is>
-      </c>
-      <c r="H149" t="n">
-        <v>391.115</v>
-      </c>
-      <c r="I149" t="n">
-        <v>391.615</v>
-      </c>
-      <c r="J149" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K149" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="n">
-        <v>144</v>
-      </c>
-      <c r="B150" t="n">
-        <v>12209</v>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>83.5%</t>
-        </is>
-      </c>
-      <c r="H150" t="n">
-        <v>395.215</v>
-      </c>
-      <c r="I150" t="n">
-        <v>395.515</v>
-      </c>
-      <c r="J150" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K150" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="n">
-        <v>145</v>
-      </c>
-      <c r="B151" t="n">
-        <v>800129</v>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>20.0%</t>
-        </is>
-      </c>
-      <c r="H151" t="n">
-        <v>395.515</v>
-      </c>
-      <c r="I151" t="n">
-        <v>395.965</v>
-      </c>
-      <c r="J151" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="K151" t="n">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="n">
-        <v>146</v>
-      </c>
-      <c r="B152" t="n">
-        <v>12237</v>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>92.5%</t>
-        </is>
-      </c>
-      <c r="H152" t="n">
-        <v>396.665</v>
-      </c>
-      <c r="I152" t="n">
-        <v>397.015</v>
-      </c>
-      <c r="J152" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K152" t="n">
-        <v>51.4</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="n">
-        <v>147</v>
-      </c>
-      <c r="B153" t="n">
-        <v>12482</v>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Public Transportation (Angkot)</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>Medium passenger vehicle</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>92.6%</t>
-        </is>
-      </c>
-      <c r="H153" t="n">
-        <v>404.964</v>
-      </c>
-      <c r="I153" t="n">
-        <v>405.364</v>
-      </c>
-      <c r="J153" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="K153" t="n">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="n">
-        <v>148</v>
-      </c>
-      <c r="B154" t="n">
-        <v>12578</v>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>83.8%</t>
-        </is>
-      </c>
-      <c r="H154" t="n">
-        <v>406.914</v>
-      </c>
-      <c r="I154" t="n">
-        <v>407.264</v>
-      </c>
-      <c r="J154" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K154" t="n">
-        <v>51.4</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="n">
-        <v>149</v>
-      </c>
-      <c r="B155" t="n">
-        <v>13012</v>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>84.7%</t>
-        </is>
-      </c>
-      <c r="H155" t="n">
-        <v>420.813</v>
-      </c>
-      <c r="I155" t="n">
-        <v>421.313</v>
-      </c>
-      <c r="J155" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="K155" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="n">
-        <v>150</v>
-      </c>
-      <c r="B156" t="n">
-        <v>13257</v>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Car / Sedan</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>Sedan / jeep / station wagon</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>88.3%</t>
-        </is>
-      </c>
-      <c r="H156" t="n">
-        <v>428.712</v>
-      </c>
-      <c r="I156" t="n">
-        <v>429.062</v>
-      </c>
-      <c r="J156" t="n">
-        <v>0.35</v>
-      </c>
-      <c r="K156" t="n">
-        <v>51.4</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="n">
-        <v>151</v>
-      </c>
-      <c r="B157" t="n">
-        <v>13309</v>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>86.3%</t>
-        </is>
-      </c>
-      <c r="H157" t="n">
-        <v>430.162</v>
-      </c>
-      <c r="I157" t="n">
-        <v>430.462</v>
-      </c>
-      <c r="J157" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="K157" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="n">
-        <v>152</v>
-      </c>
-      <c r="B158" t="n">
-        <v>800136</v>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>28.0%</t>
-        </is>
-      </c>
-      <c r="H158" t="n">
-        <v>436.311</v>
-      </c>
-      <c r="I158" t="n">
-        <v>437.511</v>
-      </c>
-      <c r="J158" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="K158" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="n">
-        <v>153</v>
-      </c>
-      <c r="B159" t="n">
-        <v>800137</v>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>33.3%</t>
-        </is>
-      </c>
-      <c r="H159" t="n">
-        <v>441.111</v>
-      </c>
-      <c r="I159" t="n">
-        <v>440.511</v>
-      </c>
-      <c r="J159" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="K159" t="n">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="n">
-        <v>154</v>
-      </c>
-      <c r="B160" t="n">
-        <v>13685</v>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>87.2%</t>
-        </is>
-      </c>
-      <c r="H160" t="n">
-        <v>441.411</v>
-      </c>
-      <c r="I160" t="n">
-        <v>441.961</v>
-      </c>
-      <c r="J160" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="K160" t="n">
-        <v>32.7</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="n">
-        <v>155</v>
-      </c>
-      <c r="B161" t="n">
-        <v>13978</v>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Motorcycle</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>Motorcycle / 3-wheel vehicle</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>opposite</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>86.7%</t>
-        </is>
-      </c>
-      <c r="H161" t="n">
-        <v>448.61</v>
-      </c>
-      <c r="I161" t="n">
-        <v>448.81</v>
-      </c>
-      <c r="J161" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="K161" t="n">
         <v>90</v>
       </c>
     </row>
